--- a/STMS_code/dist/부품_재고현황.xlsx
+++ b/STMS_code/dist/부품_재고현황.xlsx
@@ -779,8 +779,8 @@
     <col width="11.5" customWidth="1" style="29" min="12" max="12"/>
     <col width="9" customWidth="1" style="29" min="13" max="13"/>
     <col width="37.25" bestFit="1" customWidth="1" style="29" min="14" max="14"/>
-    <col width="9" customWidth="1" style="29" min="15" max="18"/>
-    <col width="9" customWidth="1" style="29" min="19" max="16384"/>
+    <col width="9" customWidth="1" style="29" min="15" max="19"/>
+    <col width="9" customWidth="1" style="29" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" s="33" thickBot="1">
@@ -867,7 +867,7 @@
       </c>
       <c r="E4" s="34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E11" s="34" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr"/>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>504</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-67</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="E18" s="35" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr"/>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E33" s="34" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>246</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr"/>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>239</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-21</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E67" s="34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-26</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">

--- a/STMS_code/dist/부품_재고현황.xlsx
+++ b/STMS_code/dist/부품_재고현황.xlsx
@@ -779,8 +779,8 @@
     <col width="11.5" customWidth="1" style="29" min="12" max="12"/>
     <col width="9" customWidth="1" style="29" min="13" max="13"/>
     <col width="37.25" bestFit="1" customWidth="1" style="29" min="14" max="14"/>
-    <col width="9" customWidth="1" style="29" min="15" max="19"/>
-    <col width="9" customWidth="1" style="29" min="20" max="16384"/>
+    <col width="9" customWidth="1" style="29" min="15" max="20"/>
+    <col width="9" customWidth="1" style="29" min="21" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" s="33" thickBot="1">
@@ -865,15 +865,11 @@
           <t>ADAPTOR_GEAR*FORCED DRIVE_DD_S45C_NONE</t>
         </is>
       </c>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="E4" s="34" t="n">
+        <v>171</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G4" s="10" t="n"/>
     </row>
@@ -898,15 +894,11 @@
           <t>Cover, HD NDEC Filter, 109x127x5t, S45C</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
-        <is>
-          <t>811</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="E5" s="34" t="n">
+        <v>810</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>200</v>
       </c>
       <c r="G5" s="10" t="n"/>
     </row>
@@ -931,12 +923,12 @@
           <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="E6" s="34" t="n">
+        <v>729</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -960,15 +952,11 @@
           <t>Slinger, HD550 Rev1 Motor Side</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="E7" s="34" t="n">
+        <v>85</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>500</v>
       </c>
       <c r="G7" s="10" t="n"/>
     </row>
@@ -993,12 +981,12 @@
           <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr"/>
+      <c r="E8" s="34" t="n">
+        <v>620</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1022,12 +1010,12 @@
           <t>Holder, HD550 Rev1 Piston Ring Motor Side</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr"/>
+      <c r="E9" s="34" t="n">
+        <v>504</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1051,15 +1039,11 @@
           <t>Holder, HD550 Rev1 Piston Ring Gear Side</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="E10" s="34" t="n">
+        <v>593</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>117</v>
       </c>
       <c r="G10" s="10" t="n"/>
     </row>
@@ -1084,12 +1068,12 @@
           <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr"/>
+      <c r="E11" s="34" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G11" s="10" t="n"/>
     </row>
     <row r="12" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1113,15 +1097,11 @@
           <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
+      <c r="E12" s="34" t="n">
+        <v>463</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>420</v>
       </c>
       <c r="G12" s="10" t="n"/>
     </row>
@@ -1146,12 +1126,12 @@
           <t>SLINGER_ID40.02*OD49.6*L15.260_S45C_NONE</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
-        <is>
-          <t>1734</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="E13" s="34" t="n">
+        <v>1733</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="21.75" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1175,15 +1155,11 @@
           <t>SLINGER_ID30.0*OD56.4*L10.1_S45C_NONE</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
+      <c r="E14" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>615</v>
       </c>
       <c r="G14" s="10" t="n"/>
     </row>
@@ -1208,12 +1184,12 @@
           <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
+      <c r="E15" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1237,12 +1213,12 @@
           <t>Oil Ring, MK700 Rev.2, S45C</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="E16" s="34" t="n">
+        <v>1294</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="10" t="n"/>
     </row>
     <row r="17" ht="21" customFormat="1" customHeight="1" s="2" thickBot="1">
@@ -1266,15 +1242,11 @@
           <t>BEARING STOPPER</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
-        <is>
-          <t>-67</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
+      <c r="E17" s="34" t="n">
+        <v>-233</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>372</v>
       </c>
       <c r="G17" s="10" t="n"/>
     </row>
@@ -1299,15 +1271,11 @@
           <t>Retainer, MK3000 Bearing</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="E18" s="35" t="n">
+        <v>154</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>300</v>
       </c>
       <c r="G18" s="10" t="n"/>
     </row>
@@ -1332,12 +1300,12 @@
           <t>OIL RING, Pusher, MK3000</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr"/>
+      <c r="E19" s="34" t="n">
+        <v>703</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G19" s="10" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1383,12 +1351,12 @@
           <t>BLOCK_TUBE SUPPORT LOWER_3/8_A6061_NONE</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
+      <c r="E22" s="34" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G22" s="10" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1412,12 +1380,12 @@
           <t>BLOCK_TUBE SUPPORT UPPER_3/8_A6061_NONE</t>
         </is>
       </c>
-      <c r="E23" s="34" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr"/>
+      <c r="E23" s="34" t="n">
+        <v>76</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G23" s="10" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1441,12 +1409,12 @@
           <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
-        <is>
-          <t>1228</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
+      <c r="E24" s="34" t="n">
+        <v>1227</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="10" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1470,12 +1438,12 @@
           <t>Plate Water Jacket Rotor Housing, DD255</t>
         </is>
       </c>
-      <c r="E25" s="37" t="inlineStr">
-        <is>
-          <t>1449</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="E25" s="37" t="n">
+        <v>1448</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G25" s="10" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1499,12 +1467,12 @@
           <t>Plate Water Jacket Rotor Housing, SUS304, DD105</t>
         </is>
       </c>
-      <c r="E26" s="37" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr"/>
+      <c r="E26" s="37" t="n">
+        <v>920</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="10" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1528,12 +1496,12 @@
           <t>Retainer, RD700 NDE Bearing</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
+      <c r="E27" s="34" t="n">
+        <v>23</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="10" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1557,15 +1525,11 @@
           <t>BEARING STOPPER</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="E28" s="34" t="n">
+        <v>221</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>500</v>
       </c>
       <c r="G28" s="10" t="n"/>
     </row>
@@ -1590,12 +1554,12 @@
           <t>OIL RING, PUSHER</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr"/>
+      <c r="E29" s="34" t="n">
+        <v>1305</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G29" s="10" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1619,12 +1583,12 @@
           <t>PUSHER-SPLASHER</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr"/>
+      <c r="E30" s="34" t="n">
+        <v>219</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G30" s="10" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1648,12 +1612,12 @@
           <t>Spacer, MK1400 Motor Rotator</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr"/>
+      <c r="E31" s="34" t="n">
+        <v>546</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" s="10" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1677,12 +1641,12 @@
           <t>Pusher, MK3000 Splasher</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr"/>
+      <c r="E32" s="34" t="n">
+        <v>266</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="10" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1706,12 +1670,12 @@
           <t>COVER-GEROTOR</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr"/>
+      <c r="E33" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="10" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1735,12 +1699,12 @@
           <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr"/>
+      <c r="E34" s="34" t="n">
+        <v>236</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="10" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1764,12 +1728,12 @@
           <t>Tongue Shim-R, MK3000</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="F35" s="10" t="inlineStr"/>
+      <c r="E35" s="34" t="n">
+        <v>224</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="10" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1789,12 +1753,12 @@
           <t>ORIFICE_PLATE*TUBE 1/4_D0.8_SUS304_NONE</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
+      <c r="E36" s="34" t="n">
+        <v>735</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="10" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1818,12 +1782,12 @@
           <t>HOLDER_PISTON RING_ID35.0*OD44.6*L16.16_12L14_NONE</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr"/>
+      <c r="E37" s="34" t="n">
+        <v>135</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="10" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1847,12 +1811,12 @@
           <t>RETAINER_BEARING_MK1400 REV-3_6207_S45C_NONE</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
-        <is>
-          <t>1089</t>
-        </is>
-      </c>
-      <c r="F38" s="10" t="inlineStr"/>
+      <c r="E38" s="34" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G38" s="10" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1876,12 +1840,12 @@
           <t>OIL RING_6214_S45C_NONE</t>
         </is>
       </c>
-      <c r="E39" s="34" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr"/>
+      <c r="E39" s="34" t="n">
+        <v>131</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G39" s="10" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1905,15 +1869,11 @@
           <t>DUCT_OIL SPLASH GEAR SIDE_WS1001_A6061_NONE</t>
         </is>
       </c>
-      <c r="E40" s="34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="E40" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>41</v>
       </c>
       <c r="G40" s="10" t="n"/>
     </row>
@@ -1938,15 +1898,11 @@
           <t>DUCT_OIL SPLASH MOTOR SIDE_WS1001_A6061_NONE</t>
         </is>
       </c>
-      <c r="E41" s="34" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="E41" s="34" t="n">
+        <v>134</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>15</v>
       </c>
       <c r="G41" s="10" t="n"/>
     </row>
@@ -1971,12 +1927,12 @@
           <t>DUCT_OIL SPLASH MOTOR SIDE_WS501_A6061_NONE</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="F42" s="10" t="inlineStr"/>
+      <c r="E42" s="34" t="n">
+        <v>161</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" s="10" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1" s="33" thickBot="1">
@@ -1996,12 +1952,12 @@
           <t>DUCT_OIL SPLASH GEAR SIDE_WS501_A6061_NONE</t>
         </is>
       </c>
-      <c r="E43" s="34" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr"/>
+      <c r="E43" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" s="10" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2021,15 +1977,11 @@
           <t>DUCT_OIL SPLASH MOTOR SIDE_WS2001_A6061_NONE</t>
         </is>
       </c>
-      <c r="E44" s="34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E44" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="G44" s="10" t="n"/>
     </row>
@@ -2050,12 +2002,12 @@
           <t>GEROTOR_SMF5030_비전분말야금</t>
         </is>
       </c>
-      <c r="E45" s="34" t="inlineStr">
-        <is>
-          <t>1850</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr"/>
+      <c r="E45" s="34" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G45" s="10" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="33" thickBot="1">
@@ -2101,12 +2053,12 @@
           <t>Slinger, HD300 DE Rotor, 20.280mm, 12L14</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="inlineStr"/>
+      <c r="E48" s="34" t="n">
+        <v>508</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G48" s="10" t="n"/>
     </row>
     <row r="49" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2130,12 +2082,12 @@
           <t>Slinger, HD300 DE Rotor, 20.320mm, 12L14</t>
         </is>
       </c>
-      <c r="E49" s="34" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F49" s="10" t="inlineStr"/>
+      <c r="E49" s="34" t="n">
+        <v>575</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G49" s="10" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2159,12 +2111,12 @@
           <t>Retainer, RD700 NDE Bearing</t>
         </is>
       </c>
-      <c r="E50" s="34" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="F50" s="10" t="inlineStr"/>
+      <c r="E50" s="34" t="n">
+        <v>452</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G50" s="10" t="n"/>
     </row>
     <row r="51" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2188,12 +2140,12 @@
           <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
-      <c r="E51" s="34" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="F51" s="10" t="inlineStr"/>
+      <c r="E51" s="34" t="n">
+        <v>273</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G51" s="10" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2217,12 +2169,12 @@
           <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
-      <c r="E52" s="34" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F52" s="10" t="inlineStr"/>
+      <c r="E52" s="34" t="n">
+        <v>115</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G52" s="10" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2246,12 +2198,12 @@
           <t>Pusher, RD900 Rotator</t>
         </is>
       </c>
-      <c r="E53" s="34" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="F53" s="10" t="inlineStr"/>
+      <c r="E53" s="34" t="n">
+        <v>155</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G53" s="10" t="n"/>
     </row>
     <row r="54" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2275,12 +2227,12 @@
           <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
-      <c r="E54" s="34" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F54" s="10" t="inlineStr"/>
+      <c r="E54" s="34" t="n">
+        <v>118</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G54" s="10" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2304,12 +2256,12 @@
           <t>PLATE_BYPASS_RD900_1-2 STAGE_SUS304_NONE</t>
         </is>
       </c>
-      <c r="E55" s="34" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr"/>
+      <c r="E55" s="34" t="n">
+        <v>91</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G55" s="10" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2333,12 +2285,12 @@
           <t>RETAINER_BEARING_5211_S45C_NONE</t>
         </is>
       </c>
-      <c r="E56" s="34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr"/>
+      <c r="E56" s="34" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G56" s="10" t="n"/>
     </row>
     <row r="57" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2362,12 +2314,12 @@
           <t>PUSHER-SPLASHER</t>
         </is>
       </c>
-      <c r="E57" s="34" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr"/>
+      <c r="E57" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G57" s="10" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2391,12 +2343,12 @@
           <t>DISC PUSHER, MOTOR KEY TYPE</t>
         </is>
       </c>
-      <c r="E58" s="34" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr"/>
+      <c r="E58" s="34" t="n">
+        <v>204</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G58" s="10" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2420,12 +2372,12 @@
           <t>Oil Feed Block, DD105-255, A6061-T6</t>
         </is>
       </c>
-      <c r="E59" s="34" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="F59" s="10" t="inlineStr"/>
+      <c r="E59" s="34" t="n">
+        <v>210</v>
+      </c>
+      <c r="F59" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G59" s="10" t="n"/>
     </row>
     <row r="60" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2449,12 +2401,12 @@
           <t>SPLASH, RING</t>
         </is>
       </c>
-      <c r="E60" s="34" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr"/>
+      <c r="E60" s="34" t="n">
+        <v>196</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G60" s="10" t="n"/>
     </row>
     <row r="61" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2478,12 +2430,12 @@
           <t>Oil Feed Block, DD 1855PW (MD000720)</t>
         </is>
       </c>
-      <c r="E61" s="34" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="F61" s="10" t="inlineStr"/>
+      <c r="E61" s="34" t="n">
+        <v>47</v>
+      </c>
+      <c r="F61" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G61" s="10" t="n"/>
     </row>
     <row r="62" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2503,12 +2455,12 @@
           <t>BLOCK_DD100KHF_BASE_A6061_NONE</t>
         </is>
       </c>
-      <c r="E62" s="34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr"/>
+      <c r="E62" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G62" s="10" t="n"/>
     </row>
     <row r="63" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2528,15 +2480,11 @@
           <t>COLUMN_SUPPORT_XD1800_OD40.0*L26.0-M8_SUS316_NONE</t>
         </is>
       </c>
-      <c r="E63" s="34" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E63" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="G63" s="10" t="n"/>
     </row>
@@ -2561,12 +2509,12 @@
           <t>SLINGER_ID40.0*D74.0*L22.0_HD2000EM_S45C_NONE</t>
         </is>
       </c>
-      <c r="E64" s="34" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr"/>
+      <c r="E64" s="34" t="n">
+        <v>46</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="10" t="n"/>
     </row>
     <row r="65" ht="21" customHeight="1" s="33" thickBot="1">
@@ -2590,12 +2538,12 @@
           <t>SLINGER_ID40.0*D74.0*L22.0_사각 GROOVE_HD2000EM_S45C_NONE</t>
         </is>
       </c>
-      <c r="E65" s="34" t="inlineStr">
-        <is>
-          <t>-21</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr"/>
+      <c r="E65" s="34" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G65" s="10" t="n"/>
     </row>
     <row r="66" ht="21.75" customHeight="1" s="33" thickBot="1">
@@ -2615,12 +2563,12 @@
           <t>BODY_I-PEL_HD550 SHAFT(Y, NDE)_G1/4''*L17_S45C_NONE</t>
         </is>
       </c>
-      <c r="E66" s="34" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr"/>
+      <c r="E66" s="34" t="n">
+        <v>48</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G66" s="10" t="n"/>
     </row>
     <row r="67" ht="21.75" customHeight="1" s="33" thickBot="1">
@@ -2640,15 +2588,11 @@
           <t>SPACER_IPEL_SPLASH DISK_HD200_A6061_NONE</t>
         </is>
       </c>
-      <c r="E67" s="34" t="inlineStr">
-        <is>
-          <t>-26</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="E67" s="34" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>63</v>
       </c>
       <c r="G67" s="10" t="n"/>
     </row>
@@ -2665,12 +2609,12 @@
       </c>
       <c r="C68" s="6" t="inlineStr"/>
       <c r="D68" s="6" t="inlineStr"/>
-      <c r="E68" s="34" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr"/>
+      <c r="E68" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G68" s="10" t="n"/>
     </row>
     <row r="69" ht="21.75" customHeight="1" s="33" thickBot="1">
@@ -2690,12 +2634,12 @@
           <t>Stud BOLT</t>
         </is>
       </c>
-      <c r="E69" s="34" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr"/>
+      <c r="E69" s="34" t="n">
+        <v>83</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="G69" s="10" t="n"/>
     </row>
     <row r="70" ht="61.5" customHeight="1" s="33" thickBot="1">
@@ -2737,12 +2681,12 @@
           <t>Adapter, HD4500 Rev2 Casting Type</t>
         </is>
       </c>
-      <c r="E71" s="34" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr"/>
+      <c r="E71" s="34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" s="7" t="n"/>
     </row>
     <row r="72" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2766,12 +2710,12 @@
           <t>Adapter, HD5500 Casting Type</t>
         </is>
       </c>
-      <c r="E72" s="34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr"/>
+      <c r="E72" s="34" t="n">
+        <v>21</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" s="7" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2795,12 +2739,12 @@
           <t>Adaptor, HD2400/3000 BP To DP Casting Type, None, GC250</t>
         </is>
       </c>
-      <c r="E73" s="37" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="E73" s="37" t="n">
+        <v>26</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G73" s="7" t="n"/>
     </row>
     <row r="74" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2824,12 +2768,12 @@
           <t>Adapter, RD3009L Casting Type</t>
         </is>
       </c>
-      <c r="E74" s="37" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
+      <c r="E74" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G74" s="7" t="n"/>
     </row>
     <row r="75" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2853,15 +2797,11 @@
           <t>Adaptor, XD1200 DP To BP Casting Type.</t>
         </is>
       </c>
-      <c r="E75" s="37" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
+      <c r="E75" s="37" t="n">
+        <v>92</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>300</v>
       </c>
       <c r="G75" s="7" t="n"/>
     </row>
@@ -2886,15 +2826,11 @@
           <t>Adaptor, HD3000 BP To DP Casting Type, None, GC250</t>
         </is>
       </c>
-      <c r="E76" s="37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="E76" s="37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="G76" s="7" t="n"/>
     </row>
@@ -2915,12 +2851,12 @@
           <t>ADAPTOR</t>
         </is>
       </c>
-      <c r="E77" s="34" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="E77" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G77" s="7" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2940,12 +2876,12 @@
           <t>ADAPTOR</t>
         </is>
       </c>
-      <c r="E78" s="34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
+      <c r="E78" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G78" s="7" t="n"/>
     </row>
     <row r="79" ht="18" customHeight="1" s="33" thickBot="1">
@@ -2965,15 +2901,11 @@
           <t>Adaptor_BP TO DP_HD3500 GEN-1_CASTING</t>
         </is>
       </c>
-      <c r="E79" s="37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
+      <c r="E79" s="37" t="n">
+        <v>40</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>167</v>
       </c>
       <c r="G79" s="7" t="n"/>
     </row>
@@ -2994,12 +2926,12 @@
           <t>ADAPTOR</t>
         </is>
       </c>
-      <c r="E80" s="37" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="E80" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G80" s="7" t="n"/>
     </row>
     <row r="81" ht="18" customHeight="1" s="33" thickBot="1">
@@ -3019,12 +2951,12 @@
           <t>ADAPTOR_BP TO DP_HD3000 GEN-1 (수리용)_CASTING_GCD450_PAINT</t>
         </is>
       </c>
-      <c r="E81" s="37" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="E81" s="37" t="n">
+        <v>57</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="G81" s="7" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1" s="33"/>

--- a/STMS_code/dist/부품_재고현황.xlsx
+++ b/STMS_code/dist/부품_재고현황.xlsx
@@ -1756,7 +1756,7 @@
           <t>MD000763</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
+      <c r="C36" s="8" t="inlineStr"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>ORIFICE_PLATE*TUBE 1/4_D0.8_SUS304_NONE</t>
@@ -1955,7 +1955,7 @@
           <t>MD001005</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
+      <c r="C43" s="6" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr">
         <is>
           <t>DUCT_OIL SPLASH GEAR SIDE_WS501_A6061_NONE</t>
@@ -1980,7 +1980,7 @@
           <t>MD001007</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n"/>
+      <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr">
         <is>
           <t>DUCT_OIL SPLASH MOTOR SIDE_WS2001_A6061_NONE</t>
@@ -2005,7 +2005,7 @@
           <t>SA000795</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n"/>
+      <c r="C45" s="6" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr">
         <is>
           <t>GEROTOR_SMF5030_비전분말야금</t>
@@ -2458,7 +2458,7 @@
           <t>MD000906</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n"/>
+      <c r="C62" s="6" t="inlineStr"/>
       <c r="D62" s="6" t="inlineStr">
         <is>
           <t>BLOCK_DD100KHF_BASE_A6061_NONE</t>
@@ -2483,7 +2483,7 @@
           <t>MD000912</t>
         </is>
       </c>
-      <c r="C63" s="6" t="n"/>
+      <c r="C63" s="6" t="inlineStr"/>
       <c r="D63" s="6" t="inlineStr">
         <is>
           <t>COLUMN_SUPPORT_XD1800_OD40.0*L26.0-M8_SUS316_NONE</t>
@@ -2566,7 +2566,7 @@
           <t>MD001174</t>
         </is>
       </c>
-      <c r="C66" s="6" t="n"/>
+      <c r="C66" s="6" t="inlineStr"/>
       <c r="D66" s="6" t="inlineStr">
         <is>
           <t>BODY_I-PEL_HD550 SHAFT(Y, NDE)_G1/4''*L17_S45C_NONE</t>
@@ -2591,7 +2591,7 @@
           <t>MD001319</t>
         </is>
       </c>
-      <c r="C67" s="6" t="n"/>
+      <c r="C67" s="6" t="inlineStr"/>
       <c r="D67" s="6" t="inlineStr">
         <is>
           <t>SPACER_IPEL_SPLASH DISK_HD200_A6061_NONE</t>
@@ -2616,8 +2616,8 @@
           <t>MD001315</t>
         </is>
       </c>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
+      <c r="C68" s="6" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
       <c r="E68" s="34" t="n">
         <v>4022</v>
       </c>
@@ -2637,7 +2637,7 @@
           <t>803A030</t>
         </is>
       </c>
-      <c r="C69" s="6" t="n"/>
+      <c r="C69" s="6" t="inlineStr"/>
       <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Stud BOLT</t>
@@ -2854,7 +2854,7 @@
           <t>MC000573</t>
         </is>
       </c>
-      <c r="C77" s="6" t="n"/>
+      <c r="C77" s="6" t="inlineStr"/>
       <c r="D77" s="6" t="inlineStr">
         <is>
           <t>ADAPTOR</t>
@@ -2879,7 +2879,7 @@
           <t>MC000574</t>
         </is>
       </c>
-      <c r="C78" s="6" t="n"/>
+      <c r="C78" s="6" t="inlineStr"/>
       <c r="D78" s="6" t="inlineStr">
         <is>
           <t>ADAPTOR</t>
@@ -2904,7 +2904,7 @@
           <t>MC000748</t>
         </is>
       </c>
-      <c r="C79" s="8" t="n"/>
+      <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="6" t="inlineStr">
         <is>
           <t>Adaptor_BP TO DP_HD3500 GEN-1_CASTING</t>
@@ -2929,7 +2929,7 @@
           <t>MC000798</t>
         </is>
       </c>
-      <c r="C80" s="8" t="n"/>
+      <c r="C80" s="8" t="inlineStr"/>
       <c r="D80" s="6" t="inlineStr">
         <is>
           <t>ADAPTOR</t>
@@ -2954,7 +2954,7 @@
           <t>MC000819</t>
         </is>
       </c>
-      <c r="C81" s="6" t="n"/>
+      <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" s="6" t="inlineStr">
         <is>
           <t>ADAPTOR_BP TO DP_HD3000 GEN-1 (수리용)_CASTING_GCD450_PAINT</t>
